--- a/InputData/trans/EoNVFEwFC/Elast of New Veh Fuel Econ wrt Fuel Cost.xlsx
+++ b/InputData/trans/EoNVFEwFC/Elast of New Veh Fuel Econ wrt Fuel Cost.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28224"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipM\InputData\trans\EoNVFEwFC\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_541BA0E32723282055D5689C0D6143CD43A1AC76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="45" windowWidth="25875" windowHeight="11310"/>
+    <workbookView xWindow="360" yWindow="45" windowWidth="25875" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,7 +26,23 @@
   <definedNames>
     <definedName name="elec_fraction">'Plug-in Hybrid Elec Fraction'!$A$5</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -68,12 +85,96 @@
     <t>Page 36</t>
   </si>
   <si>
+    <t>fraction of electricity used by plug-in hybrids</t>
+  </si>
+  <si>
+    <t>DoE Alternative Fuels Data Center</t>
+  </si>
+  <si>
+    <t>year unspecified</t>
+  </si>
+  <si>
+    <t>Hybrid and Plug-In Electric Vehicle Emissions Data Sources and Assumptions</t>
+  </si>
+  <si>
+    <t>https://www.afdc.energy.gov/vehicles/electric_emissions_sources.html</t>
+  </si>
+  <si>
+    <t>Second-to-last parameter in the table</t>
+  </si>
+  <si>
+    <t>fraction of fuel used by freight ships</t>
+  </si>
+  <si>
+    <t>See variable trans/BPoEFUbVT</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>We use elastiticies of zero for any fuel type that is not used by a given vehicle technology,</t>
+  </si>
+  <si>
+    <t>or that is not used very much by a given vehicle technology (such as the two biofuels), since</t>
+  </si>
+  <si>
+    <t>new vehicle fuel economy will be influenced only by the most common sort of fuel or fuels</t>
+  </si>
+  <si>
+    <t>burned by that vehicle and that technology type.</t>
+  </si>
+  <si>
+    <t>For plug-in hybrids, we divide the elasticity between electricity and the main combustible</t>
+  </si>
+  <si>
+    <t>fuel according to the fraction of electricity used by plug-in hybrids.</t>
+  </si>
+  <si>
+    <t>For ships, we divide the elasticity between diesel fuel and residual fuel oil according</t>
+  </si>
+  <si>
+    <t>to the fraction of each of these fuel types used by freight ships in the start year.</t>
+  </si>
+  <si>
+    <t>Plug-in hybrids can accept either electricity or combustible fuels.</t>
+  </si>
+  <si>
+    <t>This sheet specifies the percentage of driving for which electricity is used.</t>
+  </si>
+  <si>
+    <t>Electricity fraction</t>
+  </si>
+  <si>
+    <t>Our data source (DoE Alternative Fuels Data Center, as specified on the</t>
+  </si>
+  <si>
+    <t>"About" tab) includes the following source information, indicating</t>
+  </si>
+  <si>
+    <t>where they obtained their number:</t>
+  </si>
+  <si>
+    <t>Estimate based on the current industry standard, SAE J2841 (available in http://avt.inel.gov/pdf/EVProj/EVProjectUtilityFactorVolt.pdf), assuming the PHEV all-electric range is 33 miles.</t>
+  </si>
+  <si>
+    <t>Elasticities</t>
+  </si>
+  <si>
     <t>Vehicle Type</t>
   </si>
   <si>
+    <t>Elasticity</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>aircraft</t>
   </si>
   <si>
+    <t>Assumed to be the same as HDVs.</t>
+  </si>
+  <si>
     <t>rail</t>
   </si>
   <si>
@@ -83,16 +184,28 @@
     <t>motorbikes</t>
   </si>
   <si>
-    <t>Elasticity</t>
-  </si>
-  <si>
-    <t>Assumed to be the same as HDVs.</t>
-  </si>
-  <si>
     <t>Assumed to be the same as LDVs.</t>
   </si>
   <si>
-    <t>Note</t>
+    <t>Fraction of Fuel Used by Freight Ships (2017)</t>
+  </si>
+  <si>
+    <t>sum of domestic and international freight shipping</t>
+  </si>
+  <si>
+    <t>petroleum diesel</t>
+  </si>
+  <si>
+    <t>trillion BTU</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>fraction</t>
+  </si>
+  <si>
+    <t>Elasticity (dimensionless)</t>
   </si>
   <si>
     <t>battery electric vehicle</t>
@@ -110,7 +223,10 @@
     <t>plugin hybrid vehicle</t>
   </si>
   <si>
-    <t>Notes</t>
+    <t>LPG vehicle</t>
+  </si>
+  <si>
+    <t>hydrogen vehicle</t>
   </si>
   <si>
     <t>electricity</t>
@@ -122,9 +238,6 @@
     <t>petroleum gasoline</t>
   </si>
   <si>
-    <t>petroleum diesel</t>
-  </si>
-  <si>
     <t>biofuel gasoline</t>
   </si>
   <si>
@@ -134,116 +247,20 @@
     <t>jet fuel</t>
   </si>
   <si>
-    <t>We use elastiticies of zero for any fuel type that is not used by a given vehicle technology,</t>
-  </si>
-  <si>
-    <t>or that is not used very much by a given vehicle technology (such as the two biofuels), since</t>
-  </si>
-  <si>
-    <t>new vehicle fuel economy will be influenced only by the most common sort of fuel or fuels</t>
-  </si>
-  <si>
-    <t>burned by that vehicle and that technology type.</t>
-  </si>
-  <si>
-    <t>fraction of electricity used by plug-in hybrids</t>
-  </si>
-  <si>
-    <t>DoE Alternative Fuels Data Center</t>
-  </si>
-  <si>
-    <t>year unspecified</t>
-  </si>
-  <si>
-    <t>Hybrid and Plug-In Electric Vehicle Emissions Data Sources and Assumptions</t>
-  </si>
-  <si>
-    <t>https://www.afdc.energy.gov/vehicles/electric_emissions_sources.html</t>
-  </si>
-  <si>
-    <t>Second-to-last parameter in the table</t>
-  </si>
-  <si>
-    <t>Plug-in hybrids can accept either electricity or combustible fuels.</t>
-  </si>
-  <si>
-    <t>This sheet specifies the percentage of driving for which electricity is used.</t>
-  </si>
-  <si>
-    <t>Electricity fraction</t>
-  </si>
-  <si>
-    <t>Our data source (DoE Alternative Fuels Data Center, as specified on the</t>
-  </si>
-  <si>
-    <t>"About" tab) includes the following source information, indicating</t>
-  </si>
-  <si>
-    <t>where they obtained their number:</t>
-  </si>
-  <si>
-    <t>Estimate based on the current industry standard, SAE J2841 (available in http://avt.inel.gov/pdf/EVProj/EVProjectUtilityFactorVolt.pdf), assuming the PHEV all-electric range is 33 miles.</t>
-  </si>
-  <si>
-    <t>For plug-in hybrids, we divide the elasticity between electricity and the main combustible</t>
-  </si>
-  <si>
-    <t>fuel according to the fraction of electricity used by plug-in hybrids.</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
     <t>LPG propane or butane</t>
   </si>
   <si>
     <t>hydrogen</t>
-  </si>
-  <si>
-    <t>For ships, we divide the elasticity between diesel fuel and residual fuel oil according</t>
-  </si>
-  <si>
-    <t>to the fraction of each of these fuel types used by freight ships in the start year.</t>
-  </si>
-  <si>
-    <t>Elasticities</t>
-  </si>
-  <si>
-    <t>trillion BTU</t>
-  </si>
-  <si>
-    <t>Fraction of Fuel Used by Freight Ships (2017)</t>
-  </si>
-  <si>
-    <t>sum of domestic and international freight shipping</t>
-  </si>
-  <si>
-    <t>fraction</t>
-  </si>
-  <si>
-    <t>fraction of fuel used by freight ships</t>
-  </si>
-  <si>
-    <t>See variable trans/BPoEFUbVT</t>
-  </si>
-  <si>
-    <t>LPG vehicle</t>
-  </si>
-  <si>
-    <t>hydrogen vehicle</t>
-  </si>
-  <si>
-    <t>Elasticity (dimensionless)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,7 +393,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -385,9 +402,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -399,15 +413,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="9">
-    <cellStyle name="Body: normal cell" xfId="2"/>
-    <cellStyle name="Font: Calibri, 9pt regular" xfId="3"/>
-    <cellStyle name="Footnotes: top row" xfId="4"/>
-    <cellStyle name="Header: bottom row" xfId="5"/>
+    <cellStyle name="Body: normal cell" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Font: Calibri, 9pt regular" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Footnotes: top row" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Header: bottom row" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="6"/>
-    <cellStyle name="Parent row" xfId="7"/>
-    <cellStyle name="Table title" xfId="8"/>
+    <cellStyle name="Normal 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Parent row" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Table title" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -423,9 +437,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -463,9 +477,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -500,7 +514,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -535,7 +549,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -708,20 +722,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="95.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -729,150 +743,150 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" s="3">
         <v>2010</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="B12" s="3">
         <v>2012</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="B17" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="B18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="B19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="B20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="B21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="B22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="B24" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1"/>
-    <hyperlink ref="B14" r:id="rId2"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
@@ -880,48 +894,48 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>50</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -930,34 +944,34 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -965,7 +979,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -973,114 +987,114 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <f>B$4</f>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <f t="shared" ref="B6:B7" si="0">B$4</f>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <f>B$3</f>
         <v>0.1</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <f>522+285</f>
         <v>807</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <f>3+675</f>
         <v>678</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="11">
+        <v>48</v>
+      </c>
+      <c r="B18" s="10">
         <f>B15/SUM(B$15:B$16)</f>
         <v>0.54343434343434338</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="11">
+        <v>50</v>
+      </c>
+      <c r="B19" s="10">
         <f>B16/SUM(B$15:B$16)</f>
         <v>0.45656565656565656</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1090,12 +1104,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -1105,35 +1119,35 @@
     <col min="6" max="8" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <f>Data!$B$3</f>
@@ -1159,9 +1173,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1186,9 +1200,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1214,9 +1228,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1241,9 +1255,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1267,9 +1281,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1293,9 +1307,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1319,9 +1333,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1345,9 +1359,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1372,9 +1386,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1406,12 +1420,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -1421,35 +1435,35 @@
     <col min="6" max="8" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <f>Data!$B$4</f>
@@ -1475,9 +1489,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1502,9 +1516,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1529,9 +1543,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1557,9 +1571,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1583,9 +1597,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1609,9 +1623,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1635,9 +1649,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1661,9 +1675,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1688,9 +1702,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1722,12 +1736,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -1737,35 +1751,35 @@
     <col min="6" max="8" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <f>Data!$B$5</f>
@@ -1790,9 +1804,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1817,9 +1831,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1844,9 +1858,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1870,9 +1884,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1896,9 +1910,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1922,9 +1936,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1949,9 +1963,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1975,9 +1989,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2001,9 +2015,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2035,12 +2049,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -2050,35 +2064,35 @@
     <col min="6" max="8" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <f>Data!$B$6</f>
@@ -2103,9 +2117,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2130,9 +2144,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2157,9 +2171,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2184,9 +2198,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2210,9 +2224,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2236,9 +2250,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2262,9 +2276,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2288,9 +2302,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2314,9 +2328,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2348,12 +2362,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -2363,35 +2377,35 @@
     <col min="6" max="8" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <f>Data!$B$7</f>
@@ -2416,9 +2430,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2443,9 +2457,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2470,9 +2484,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2497,9 +2511,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2523,9 +2537,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2549,9 +2563,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2575,9 +2589,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2602,9 +2616,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2628,9 +2642,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2662,12 +2676,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -2677,35 +2691,35 @@
     <col min="6" max="8" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <f>Data!$B$8</f>
@@ -2731,9 +2745,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2758,9 +2772,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2786,9 +2800,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2813,9 +2827,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2839,9 +2853,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2865,9 +2879,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2891,9 +2905,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2917,9 +2931,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2944,9 +2958,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2975,4 +2989,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7195459E-DDB9-41ED-BC76-FF562B6FAC93}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD232688-AE27-4390-80FD-C08A9F20F73D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7974A4F-7E70-49E8-9C3D-0E7D2D2EEA1B}"/>
 </file>